--- a/solution_output.xlsx
+++ b/solution_output.xlsx
@@ -7,16 +7,33 @@
     <workbookView xWindow="240" yWindow="15" windowWidth="16095" windowHeight="9660"/>
   </bookViews>
   <sheets>
-    <sheet name="AC1" sheetId="1" r:id="rId1"/>
-    <sheet name="AC2" sheetId="2" r:id="rId2"/>
-    <sheet name="AC3" sheetId="3" r:id="rId3"/>
+    <sheet name="AC_A_1" sheetId="1" r:id="rId1"/>
+    <sheet name="AC_A_2" sheetId="2" r:id="rId2"/>
+    <sheet name="AC_A_3" sheetId="3" r:id="rId3"/>
+    <sheet name="AC_A_4" sheetId="4" r:id="rId4"/>
+    <sheet name="AC_A_5" sheetId="5" r:id="rId5"/>
+    <sheet name="AC_A_6" sheetId="6" r:id="rId6"/>
+    <sheet name="AC_A_7" sheetId="7" r:id="rId7"/>
+    <sheet name="AC_A_8" sheetId="8" r:id="rId8"/>
+    <sheet name="AC_A_9" sheetId="9" r:id="rId9"/>
+    <sheet name="AC_A_10" sheetId="10" r:id="rId10"/>
+    <sheet name="AC_D_1" sheetId="11" r:id="rId11"/>
+    <sheet name="AC_D_2" sheetId="12" r:id="rId12"/>
+    <sheet name="AC_D_3" sheetId="13" r:id="rId13"/>
+    <sheet name="AC_D_4" sheetId="14" r:id="rId14"/>
+    <sheet name="AC_D_5" sheetId="15" r:id="rId15"/>
+    <sheet name="AC_D_6" sheetId="16" r:id="rId16"/>
+    <sheet name="AC_D_7" sheetId="17" r:id="rId17"/>
+    <sheet name="AC_D_8" sheetId="18" r:id="rId18"/>
+    <sheet name="AC_D_9" sheetId="19" r:id="rId19"/>
+    <sheet name="AC_D_10" sheetId="20" r:id="rId20"/>
   </sheets>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="26" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="15">
   <si>
     <t>Node</t>
   </si>
@@ -439,7 +456,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>100</v>
+        <v>0</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -447,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>120.4899377460533</v>
+        <v>20.48993774616611</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -455,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>139.9283994638826</v>
+        <v>39.92839916451885</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -463,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>159.3668611817118</v>
+        <v>59.36686085929978</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -471,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>172.3258356602452</v>
+        <v>72.32583533789148</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -479,15 +496,15 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>178.8053228995119</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+        <v>78.8053224049745</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
   <dimension ref="A1:B8"/>
   <sheetFormatPr defaultRowHeight="15"/>
@@ -510,7 +527,7 @@
         <v>2</v>
       </c>
       <c r="B3">
-        <v>200</v>
+        <v>810</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -518,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>220.4899377460532</v>
+        <v>830.4899376321046</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -526,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>239.9283994638825</v>
+        <v>849.9283993499994</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -534,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>259.3668611817117</v>
+        <v>869.3668610678978</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -542,7 +559,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>272.3258356602451</v>
+        <v>882.3258355464932</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -550,7 +567,708 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>278.8053228995117</v>
+        <v>888.805322785789</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>51.47948723929585</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>64.43846171788755</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>109.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>129.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>96.47948723929585</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>109.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>154.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>174.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>186.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>199.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>244.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>264.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>276.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>289.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>334.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>354.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>366.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>379.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>424.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>444.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>456.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>469.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>514.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>534.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>546.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>559.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>604.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>624.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>636.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>649.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>694.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>714.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>726.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>739.4384617178875</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>784.7948723929585</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>804.233334110846</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>90</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>110.4899376815229</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>129.9283993583977</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>149.366860905473</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>162.3258353840647</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>168.8053226233606</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>810</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>816.4794872392958</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>829.4384617179021</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>874.7948723930167</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>894.2333341109043</v>
       </c>
     </row>
   </sheetData>
@@ -560,60 +1278,494 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>156.4794872392666</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>169.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>214.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>234.233334110846</v>
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>200.4899377461679</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>219.9283993242298</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>239.3668610421173</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>252.325835520709</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>258.8053222674043</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>270</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>290.4899377461697</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>309.9283994640573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>329.3668611819558</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>342.3258356605511</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>348.8053228998469</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>360</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>380.4899377461697</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>399.9283994640464</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>419.3668611819303</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>432.325835660522</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>438.805322899817</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>450</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>470.4899373473763</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>489.9283990652639</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>509.3668607831403</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>522.3258352420962</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>528.8053223443421</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>540</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>560.4899377461679</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>579.9283990635759</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>599.3668607814616</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>612.3258352600533</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>618.8053223401948</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>630</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>650.4899375165623</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>669.9283992344281</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>689.3668609523156</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>702.3258354309073</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>708.8053226702032</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
+        <v>720</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>3</v>
+      </c>
+      <c r="B4">
+        <v>740.4899377461697</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>4</v>
+      </c>
+      <c r="B5">
+        <v>759.9283994640573</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>5</v>
+      </c>
+      <c r="B6">
+        <v>779.3668611819448</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>6</v>
+      </c>
+      <c r="B7">
+        <v>792.3258356605365</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2">
+      <c r="A8" t="s">
+        <v>7</v>
+      </c>
+      <c r="B8">
+        <v>798.8053228998324</v>
       </c>
     </row>
   </sheetData>

--- a/solution_output.xlsx
+++ b/solution_output.xlsx
@@ -464,7 +464,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>20.48993774616611</v>
+        <v>20.48993774616972</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -472,7 +472,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>39.92839916451885</v>
+        <v>39.92839946393951</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -480,7 +480,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>59.36686085929978</v>
+        <v>59.3668611805042</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -488,7 +488,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>72.32583533789148</v>
+        <v>72.3258356590959</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -496,7 +496,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>78.8053224049745</v>
+        <v>78.80532289600524</v>
       </c>
     </row>
   </sheetData>
@@ -535,7 +535,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>830.4899376321046</v>
+        <v>830.4899377445145</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -543,7 +543,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>849.9283993499994</v>
+        <v>849.928399462402</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -551,7 +551,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>869.3668610678978</v>
+        <v>869.3668611802896</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -559,7 +559,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>882.3258355464932</v>
+        <v>882.3258356588813</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -567,7 +567,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>888.805322785789</v>
+        <v>888.8053228981771</v>
       </c>
     </row>
   </sheetData>
@@ -606,7 +606,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>51.47948723929585</v>
+        <v>51.47948723914999</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -614,7 +614,7 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>64.43846171788755</v>
+        <v>64.43846171761106</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -622,7 +622,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>109.7948723929585</v>
+        <v>109.7948723925365</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -630,7 +630,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>129.233334110846</v>
+        <v>149.3668611819332</v>
       </c>
     </row>
   </sheetData>
@@ -661,519 +661,519 @@
         <v>9</v>
       </c>
       <c r="B3">
+        <v>135</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>141.4794872385573</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>154.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>199.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>239.3668611810726</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>225</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>231.4794872385464</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>244.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>289.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>329.3668611819448</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>315</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>321.4794872382736</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>334.4384617176693</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>379.7948723925947</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>419.3668611810726</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>405</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>411.4794872384373</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>424.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>469.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>528.3668611810722</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>495</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>501.4794872386337</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>514.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>559.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>599.3668611811863</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>585</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>591.4794872383936</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>604.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>649.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>709.3668611811856</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>675</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>681.4794872384664</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>694.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>739.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>779.3668611812209</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B7"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>9</v>
+      </c>
+      <c r="B3">
+        <v>765</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2">
+      <c r="A4" t="s">
+        <v>10</v>
+      </c>
+      <c r="B4">
+        <v>771.4794872386046</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2">
+      <c r="A5" t="s">
+        <v>11</v>
+      </c>
+      <c r="B5">
+        <v>784.4384617177275</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2">
+      <c r="A6" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6">
+        <v>829.7948723926529</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2">
+      <c r="A7" t="s">
+        <v>13</v>
+      </c>
+      <c r="B7">
+        <v>869.3668611814101</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <dimension ref="A1:B8"/>
+  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetData>
+    <row r="1" spans="1:2">
+      <c r="A1" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2">
+      <c r="A2" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2">
+      <c r="A3" t="s">
+        <v>2</v>
+      </c>
+      <c r="B3">
         <v>90</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>96.47948723929585</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>109.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>154.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>174.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>180</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>186.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>199.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>244.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>264.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>270</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>276.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>289.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>334.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>354.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>360</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>366.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>379.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>424.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>444.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>450</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>456.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>469.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>514.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>534.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>540</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>546.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>559.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>604.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>624.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>630</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>636.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>649.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>694.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>714.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B7"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>14</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>9</v>
-      </c>
-      <c r="B3">
-        <v>720</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
-        <v>10</v>
-      </c>
-      <c r="B4">
-        <v>726.4794872392958</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2">
-      <c r="A5" t="s">
-        <v>11</v>
-      </c>
-      <c r="B5">
-        <v>739.4384617178875</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2">
-      <c r="A6" t="s">
-        <v>12</v>
-      </c>
-      <c r="B6">
-        <v>784.7948723929585</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2">
-      <c r="A7" t="s">
-        <v>13</v>
-      </c>
-      <c r="B7">
-        <v>804.233334110846</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
-  <sheetFormatPr defaultRowHeight="15"/>
-  <sheetData>
-    <row r="1" spans="1:2">
-      <c r="A1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2">
-      <c r="A2" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2">
-      <c r="A3" t="s">
-        <v>2</v>
-      </c>
-      <c r="B3">
-        <v>90</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2">
-      <c r="A4" t="s">
         <v>3</v>
       </c>
       <c r="B4">
-        <v>110.4899376815229</v>
+        <v>110.489937746158</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1181,7 +1181,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>129.9283993583977</v>
+        <v>129.9283994640456</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1189,7 +1189,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>149.366860905473</v>
+        <v>149.3668611819332</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1197,7 +1197,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>162.3258353840647</v>
+        <v>162.3258356605248</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1205,7 +1205,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>168.8053226233606</v>
+        <v>168.8053228998207</v>
       </c>
     </row>
   </sheetData>
@@ -1236,7 +1236,7 @@
         <v>9</v>
       </c>
       <c r="B3">
-        <v>810</v>
+        <v>855</v>
       </c>
     </row>
     <row r="4" spans="1:2">
@@ -1244,7 +1244,7 @@
         <v>10</v>
       </c>
       <c r="B4">
-        <v>816.4794872392958</v>
+        <v>861.4794872391358</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1252,7 +1252,7 @@
         <v>11</v>
       </c>
       <c r="B5">
-        <v>829.4384617179021</v>
+        <v>874.4384617177275</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1260,7 +1260,7 @@
         <v>12</v>
       </c>
       <c r="B6">
-        <v>874.7948723930167</v>
+        <v>919.7948723926238</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1268,7 +1268,7 @@
         <v>13</v>
       </c>
       <c r="B7">
-        <v>894.2333341109043</v>
+        <v>939.2333341105114</v>
       </c>
     </row>
   </sheetData>
@@ -1307,7 +1307,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>200.4899377461679</v>
+        <v>200.4899377458785</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1315,7 +1315,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>219.9283993242298</v>
+        <v>219.9283994598627</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1323,7 +1323,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>239.3668610421173</v>
+        <v>239.3668611777503</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1331,7 +1331,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>252.325835520709</v>
+        <v>252.325835656342</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1339,7 +1339,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>258.8053222674043</v>
+        <v>258.8053228956378</v>
       </c>
     </row>
   </sheetData>
@@ -1394,7 +1394,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>329.3668611819558</v>
+        <v>329.3668611819448</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1402,7 +1402,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>342.3258356605511</v>
+        <v>342.3258356605365</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1410,7 +1410,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>348.8053228998469</v>
+        <v>348.8053228998324</v>
       </c>
     </row>
   </sheetData>
@@ -1449,7 +1449,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>380.4899377461697</v>
+        <v>380.4899377458783</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1457,7 +1457,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>399.9283994640464</v>
+        <v>399.9283994599355</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1465,7 +1465,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>419.3668611819303</v>
+        <v>419.366861177823</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1473,7 +1473,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>432.325835660522</v>
+        <v>432.3258356564147</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1481,7 +1481,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>438.805322899817</v>
+        <v>438.8053228957106</v>
       </c>
     </row>
   </sheetData>
@@ -1520,7 +1520,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>470.4899373473763</v>
+        <v>470.4899377458875</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1528,7 +1528,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>489.9283990652639</v>
+        <v>489.9283994599537</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1536,7 +1536,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>509.3668607831403</v>
+        <v>509.3668611778412</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1544,7 +1544,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>522.3258352420962</v>
+        <v>522.3258356564329</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1552,7 +1552,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>528.8053223443421</v>
+        <v>528.8053228957288</v>
       </c>
     </row>
   </sheetData>
@@ -1591,7 +1591,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>560.4899377461679</v>
+        <v>560.4899377458783</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1599,7 +1599,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>579.9283990635759</v>
+        <v>579.9283994607395</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1607,7 +1607,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>599.3668607814616</v>
+        <v>599.366861178627</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1615,7 +1615,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>612.3258352600533</v>
+        <v>612.3258356572187</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1623,7 +1623,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>618.8053223401948</v>
+        <v>618.8053228965146</v>
       </c>
     </row>
   </sheetData>
@@ -1662,7 +1662,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>650.4899375165623</v>
+        <v>650.4899377458781</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1670,7 +1670,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>669.9283992344281</v>
+        <v>669.9283994636453</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1678,7 +1678,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>689.3668609523156</v>
+        <v>689.3668611812036</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1686,7 +1686,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>702.3258354309073</v>
+        <v>702.3258356590331</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1694,7 +1694,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>708.8053226702032</v>
+        <v>708.8053228965546</v>
       </c>
     </row>
   </sheetData>
@@ -1733,7 +1733,7 @@
         <v>3</v>
       </c>
       <c r="B4">
-        <v>740.4899377461697</v>
+        <v>740.4899377458779</v>
       </c>
     </row>
     <row r="5" spans="1:2">
@@ -1741,7 +1741,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>759.9283994640573</v>
+        <v>759.9283994603902</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -1749,7 +1749,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>779.3668611819448</v>
+        <v>779.3668611782778</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -1757,7 +1757,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>792.3258356605365</v>
+        <v>792.3258356568695</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -1765,7 +1765,7 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>798.8053228998324</v>
+        <v>798.8053228961653</v>
       </c>
     </row>
   </sheetData>

--- a/solution_output.xlsx
+++ b/solution_output.xlsx
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="15">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="200" uniqueCount="24">
   <si>
     <t>Node</t>
   </si>
@@ -53,22 +53,49 @@
     <t>l5</t>
   </si>
   <si>
-    <t>k5</t>
-  </si>
-  <si>
-    <t>d4</t>
+    <t>l4</t>
+  </si>
+  <si>
+    <t>l3</t>
+  </si>
+  <si>
+    <t>l2</t>
+  </si>
+  <si>
+    <t>k2</t>
+  </si>
+  <si>
+    <t>d1</t>
   </si>
   <si>
     <t>Chosen route: route_arr_2a</t>
   </si>
   <si>
-    <t>d1</t>
-  </si>
-  <si>
-    <t>k2</t>
-  </si>
-  <si>
-    <t>l2</t>
+    <t>a1</t>
+  </si>
+  <si>
+    <t>p2</t>
+  </si>
+  <si>
+    <t>p3</t>
+  </si>
+  <si>
+    <t>p5</t>
+  </si>
+  <si>
+    <t>17rf</t>
+  </si>
+  <si>
+    <t>l6</t>
+  </si>
+  <si>
+    <t>k6</t>
+  </si>
+  <si>
+    <t>d5</t>
+  </si>
+  <si>
+    <t>Chosen route: route_arr_1b</t>
   </si>
   <si>
     <t>l1</t>
@@ -435,12 +462,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>11</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -472,7 +499,7 @@
         <v>4</v>
       </c>
       <c r="B5">
-        <v>39.92839946393951</v>
+        <v>39.92839946396975</v>
       </c>
     </row>
     <row r="6" spans="1:2">
@@ -480,7 +507,7 @@
         <v>5</v>
       </c>
       <c r="B6">
-        <v>59.3668611805042</v>
+        <v>59.3668611818216</v>
       </c>
     </row>
     <row r="7" spans="1:2">
@@ -488,7 +515,7 @@
         <v>6</v>
       </c>
       <c r="B7">
-        <v>72.3258356590959</v>
+        <v>85.28481013899113</v>
       </c>
     </row>
     <row r="8" spans="1:2">
@@ -496,7 +523,31 @@
         <v>7</v>
       </c>
       <c r="B8">
-        <v>78.80532289600524</v>
+        <v>111.2027590961602</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>8</v>
+      </c>
+      <c r="B9">
+        <v>137.1207080533168</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>9</v>
+      </c>
+      <c r="B10">
+        <v>150.0796825318425</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>10</v>
+      </c>
+      <c r="B11">
+        <v>156.5591697709733</v>
       </c>
     </row>
   </sheetData>
@@ -506,12 +557,12 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -524,7 +575,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>810</v>
@@ -532,42 +583,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>830.4899377445145</v>
+        <v>830.4899377461588</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>849.928399462402</v>
+        <v>856.4078867032931</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>869.3668611802896</v>
+        <v>882.3258356604765</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>882.3258356588813</v>
+        <v>914.7232718569849</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>888.8053228981771</v>
+        <v>934.1617335748724</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>953.60019529276</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>966.5591697713517</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>973.0386570106475</v>
       </c>
     </row>
   </sheetData>
@@ -582,7 +657,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -595,7 +670,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>45</v>
@@ -603,34 +678,34 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>51.47948723914999</v>
+        <v>51.4794872390612</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>64.43846171761106</v>
+        <v>64.4384617149758</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>109.7948723925365</v>
+        <v>109.7948723926775</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>149.3668611819332</v>
+        <v>129.2333341105514</v>
       </c>
     </row>
   </sheetData>
@@ -645,7 +720,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -658,42 +733,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>135</v>
+        <v>159.4749390285819</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>141.4794872385573</v>
+        <v>165.9544262678776</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>154.4384617177275</v>
+        <v>178.9134007464691</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>199.7948723926529</v>
+        <v>224.2698114215689</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>239.3668611810726</v>
+        <v>243.7082731394562</v>
       </c>
     </row>
   </sheetData>
@@ -708,7 +783,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -721,42 +796,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>225</v>
+        <v>237.3668611792219</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>231.4794872385464</v>
+        <v>243.8463484185182</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>244.4384617177275</v>
+        <v>256.8053228971104</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>289.7948723926529</v>
+        <v>302.1617335722111</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>329.3668611819448</v>
+        <v>331.708273139456</v>
       </c>
     </row>
   </sheetData>
@@ -771,7 +846,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -784,42 +859,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>315</v>
+        <v>329.3668611719598</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>321.4794872382736</v>
+        <v>335.8463484112562</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>334.4384617176693</v>
+        <v>348.8053228898486</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>379.7948723925947</v>
+        <v>394.1617335649495</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>419.3668611810726</v>
+        <v>413.6001952828379</v>
       </c>
     </row>
   </sheetData>
@@ -834,7 +909,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -847,42 +922,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>405</v>
+        <v>438.3668611719426</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>411.4794872384373</v>
+        <v>444.8463484112392</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>424.4384617177275</v>
+        <v>457.805322889832</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>469.7948723926529</v>
+        <v>503.1617335649332</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>528.3668611810722</v>
+        <v>522.6001952828218</v>
       </c>
     </row>
   </sheetData>
@@ -897,7 +972,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -910,42 +985,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>495</v>
+        <v>497.3668611719424</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>501.4794872386337</v>
+        <v>503.8463484112391</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>514.4384617177275</v>
+        <v>516.8053228898316</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>559.7948723926529</v>
+        <v>562.1617335649324</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>599.3668611811863</v>
+        <v>593.6001952907717</v>
       </c>
     </row>
   </sheetData>
@@ -960,7 +1035,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -973,42 +1048,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>585</v>
+        <v>607.3668611719376</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>591.4794872383936</v>
+        <v>613.8463484112345</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>604.4384617177275</v>
+        <v>626.8053228898278</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>649.7948723926529</v>
+        <v>672.1617335649298</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>709.3668611811856</v>
+        <v>703.6001952907709</v>
       </c>
     </row>
   </sheetData>
@@ -1023,7 +1098,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1036,42 +1111,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>675</v>
+        <v>689.3668611814273</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>681.4794872384664</v>
+        <v>695.846348420724</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>694.4384617177275</v>
+        <v>708.8053228993165</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>739.7948723926529</v>
+        <v>754.1617335744174</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>779.3668611812209</v>
+        <v>773.6001952923068</v>
       </c>
     </row>
   </sheetData>
@@ -1086,7 +1161,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1099,7 +1174,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
         <v>765</v>
@@ -1107,34 +1182,34 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>771.4794872386046</v>
+        <v>771.4794872392522</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>784.4384617177275</v>
+        <v>784.4384617156174</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>829.7948723926529</v>
+        <v>829.7948723900481</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>869.3668611814101</v>
+        <v>863.6001952826377</v>
       </c>
     </row>
   </sheetData>
@@ -1144,12 +1219,12 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1162,7 +1237,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>90</v>
@@ -1170,42 +1245,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>110.489937746158</v>
+        <v>110.4899377458786</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>129.9283994640456</v>
+        <v>136.407886703062</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>149.3668611819332</v>
+        <v>162.3258356599833</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>162.3258356605248</v>
+        <v>194.7232718563503</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>168.8053228998207</v>
+        <v>214.1617335740091</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>233.6001952917827</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>246.5591697702687</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>253.038657009387</v>
       </c>
     </row>
   </sheetData>
@@ -1220,7 +1319,7 @@
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>14</v>
+        <v>23</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1233,42 +1332,42 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="B3">
-        <v>855</v>
+        <v>869.3668611818835</v>
       </c>
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="B4">
-        <v>861.4794872391358</v>
+        <v>875.8463484211793</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>11</v>
+        <v>8</v>
       </c>
       <c r="B5">
-        <v>874.4384617177275</v>
+        <v>888.805322899771</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>12</v>
+        <v>21</v>
       </c>
       <c r="B6">
-        <v>919.7948723926238</v>
+        <v>934.1617335748711</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>13</v>
+        <v>22</v>
       </c>
       <c r="B7">
-        <v>939.2333341105114</v>
+        <v>953.6001952927586</v>
       </c>
     </row>
   </sheetData>
@@ -1278,12 +1377,12 @@
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1296,7 +1395,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>180</v>
@@ -1304,42 +1403,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>200.4899377458785</v>
+        <v>200.4899377458784</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>219.9283994598627</v>
+        <v>226.4078867030618</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>239.3668611777503</v>
+        <v>252.3258356598083</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>252.325835656342</v>
+        <v>284.7232718563367</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>258.8053228956378</v>
+        <v>304.1617335739877</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>323.6001952844392</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>336.559169762797</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>343.0386570011995</v>
       </c>
     </row>
   </sheetData>
@@ -1349,12 +1472,12 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1367,7 +1490,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>270</v>
@@ -1375,42 +1498,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>290.4899377461697</v>
+        <v>290.489937745853</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>309.9283994640573</v>
+        <v>316.4078867030364</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>329.3668611819448</v>
+        <v>342.3258356589062</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>342.3258356605365</v>
+        <v>374.7232718552945</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>348.8053228998324</v>
+        <v>394.1617335707987</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>413.6001952911706</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>426.5591697695352</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>433.0386570080545</v>
       </c>
     </row>
   </sheetData>
@@ -1420,12 +1567,12 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1438,7 +1585,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>360</v>
@@ -1446,42 +1593,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>380.4899377458783</v>
+        <v>380.4899377458784</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>399.9283994599355</v>
+        <v>406.4078867030618</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>419.366861177823</v>
+        <v>432.3258356600406</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>432.3258356564147</v>
+        <v>464.7232718564751</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>438.8053228957106</v>
+        <v>484.1617335741842</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>503.6001952919587</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>516.5591697704556</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>523.0386570095156</v>
       </c>
     </row>
   </sheetData>
@@ -1491,12 +1662,12 @@
 
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1509,7 +1680,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>450</v>
@@ -1517,42 +1688,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>470.4899377458875</v>
+        <v>470.4899377459555</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>489.9283994599537</v>
+        <v>496.4078867031389</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>509.3668611778412</v>
+        <v>522.3258356600692</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>522.3258356564329</v>
+        <v>554.7232718564513</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>528.8053228957288</v>
+        <v>574.1617335738025</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>593.6001952907718</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>606.5591697704658</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>613.0386570068949</v>
       </c>
     </row>
   </sheetData>
@@ -1562,12 +1757,12 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1580,7 +1775,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>540</v>
@@ -1588,42 +1783,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>560.4899377458783</v>
+        <v>560.4899377458784</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>579.9283994607395</v>
+        <v>586.4078867030618</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>599.366861178627</v>
+        <v>612.3258356598491</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>612.3258356572187</v>
+        <v>644.7232718563104</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>618.8053228965146</v>
+        <v>664.1617335726448</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>683.6001952904185</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>696.5591697687289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>703.0386570074197</v>
       </c>
     </row>
   </sheetData>
@@ -1633,12 +1852,12 @@
 
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1651,7 +1870,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>630</v>
@@ -1659,42 +1878,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>650.4899377458781</v>
+        <v>650.4899377459474</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>669.9283994636453</v>
+        <v>676.4078867031308</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>689.3668611812036</v>
+        <v>702.3258356600692</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>702.3258356590331</v>
+        <v>734.7232718555365</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>708.8053228965546</v>
+        <v>754.1617335732444</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>773.6001952554989</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>786.5591697198834</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>793.0386569374823</v>
       </c>
     </row>
   </sheetData>
@@ -1704,12 +1947,12 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B8"/>
+  <dimension ref="A1:B11"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" spans="1:2">
       <c r="A1" t="s">
-        <v>8</v>
+        <v>20</v>
       </c>
     </row>
     <row r="2" spans="1:2">
@@ -1722,7 +1965,7 @@
     </row>
     <row r="3" spans="1:2">
       <c r="A3" t="s">
-        <v>2</v>
+        <v>12</v>
       </c>
       <c r="B3">
         <v>720</v>
@@ -1730,42 +1973,66 @@
     </row>
     <row r="4" spans="1:2">
       <c r="A4" t="s">
-        <v>3</v>
+        <v>13</v>
       </c>
       <c r="B4">
-        <v>740.4899377458779</v>
+        <v>740.4899377459623</v>
       </c>
     </row>
     <row r="5" spans="1:2">
       <c r="A5" t="s">
-        <v>4</v>
+        <v>14</v>
       </c>
       <c r="B5">
-        <v>759.9283994603902</v>
+        <v>766.4078867031457</v>
       </c>
     </row>
     <row r="6" spans="1:2">
       <c r="A6" t="s">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c r="B6">
-        <v>779.3668611782778</v>
+        <v>792.3258356600393</v>
       </c>
     </row>
     <row r="7" spans="1:2">
       <c r="A7" t="s">
-        <v>6</v>
+        <v>15</v>
       </c>
       <c r="B7">
-        <v>792.3258356568695</v>
+        <v>824.7232718559389</v>
       </c>
     </row>
     <row r="8" spans="1:2">
       <c r="A8" t="s">
-        <v>7</v>
+        <v>16</v>
       </c>
       <c r="B8">
-        <v>798.8053228961653</v>
+        <v>844.1617335741175</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2">
+      <c r="A9" t="s">
+        <v>17</v>
+      </c>
+      <c r="B9">
+        <v>863.6001952826391</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2">
+      <c r="A10" t="s">
+        <v>18</v>
+      </c>
+      <c r="B10">
+        <v>876.5591697571945</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2">
+      <c r="A11" t="s">
+        <v>19</v>
+      </c>
+      <c r="B11">
+        <v>883.0386569918774</v>
       </c>
     </row>
   </sheetData>
